--- a/app/Archivos/Template/Template_HRC_copi.xlsx
+++ b/app/Archivos/Template/Template_HRC_copi.xlsx
@@ -539,7 +539,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="76" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reduc Factura Compra PMP1276670 </t>
+          <t>Reduc Factura Compra PMP1276670</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276992 UNILEVER ANDINA COLOMBIA LTDA/conciliaicon</t>
+          <t>Reduc Factura Compra PMP1276992</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1276671</t>
+          <t>Reduc Factura Compra PMP1276671</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1277137</t>
+          <t>Reduc Factura Compra PMP1277137</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1276991</t>
+          <t>Reduc Factura Compra PMP1276991</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1273112</t>
+          <t>Reduc Factura Compra PMP1273112</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1273878</t>
+          <t>Reduc Factura Compra PMP1273878</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1276666</t>
+          <t>Reduc Factura Compra PMP1276666</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1276668</t>
+          <t>Reduc Factura Compra PMP1276668</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1276990</t>
+          <t>Reduc Factura Compra PMP1276990</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1277143</t>
+          <t>Reduc Factura Compra PMP1277143</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1277142</t>
+          <t>Reduc Factura Compra PMP1277142</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>Saldo FC PMP1276988</t>
+          <t>Reduc Factura Compra PMP1276988</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>Nota AUT.G.COMERCIAL Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>Nota AUT.G.COMERCIAL Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>Nota AUT.G.COMERCIAL Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>Nota AUT.G.COMERCIAL Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>Nota nan DDPD UNILEVER MIN 2Q 2025</t>
+          <t>DDPD UNILEVER MIN 2Q 2025</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>Nota NOTA DEVOLUCIÓN NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>Nota C. UNILEVER DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</t>
+          <t>DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1276670 </t>
+          <t>Factura Acrededor PMP1276670</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277139 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>Factura Acrededor PMP1277139</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276992 UNILEVER ANDINA COLOMBIA LTDA/conciliaicon</t>
+          <t>Factura Acrededor PMP1276992</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1276671 </t>
+          <t>Factura Acrededor PMP1276671</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276991 UNILEVER ANDINA COLOMBIA LTDA/conciliacion</t>
+          <t>Factura Acrededor PMP1276991</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277137 UNILEVER ANDINA COLOMBIA LTDA/conciliacion</t>
+          <t>Factura Acrededor PMP1277137</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1273112 UNILEVER ANDINA COLOMBIA LTDA/CONCILIACION</t>
+          <t>Factura Acrededor PMP1273112</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1273596 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>Factura Acrededor PMP1273596</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1273863 </t>
+          <t>Factura Acrededor PMP1273863</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1273878 UNILEVER ANDINA COLOMBIA LTDA/CONCILIACION</t>
+          <t>Factura Acrededor PMP1273878</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1276669 </t>
+          <t>Factura Acrededor PMP1276669</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277138 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>Factura Acrededor PMP1277138</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276993 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>Factura Acrededor PMP1276993</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1276666 </t>
+          <t>Factura Acrededor PMP1276666</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1276672 </t>
+          <t>Factura Acrededor PMP1276672</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1276673 </t>
+          <t>Factura Acrededor PMP1276673</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factura Acrededor PMP1276668 </t>
+          <t>Factura Acrededor PMP1276668</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277145 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>Factura Acrededor PMP1277145</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277144 UNILEVER ANDINA COLOMBIA LTDA</t>
+          <t>Factura Acrededor PMP1277144</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276990 UNILEVER ANDINA COLOMBIA LTDA/CONCILIAICION</t>
+          <t>Factura Acrededor PMP1276990</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277143 UNILEVER ANDINA COLOMBIA LTDA/CONCILIACION</t>
+          <t>Factura Acrededor PMP1277143</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277142 UNILEVER ANDINA COLOMBIA LTDA/CONCILIACION</t>
+          <t>Factura Acrededor PMP1277142</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276988 UNILEVER ANDINA COLOMBIA LTDA/CONCILIACION</t>
+          <t>Factura Acrededor PMP1276988</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devolucion 5009108214 </t>
+          <t>Devolucion 5009108214</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devolucion 5009109080 </t>
+          <t>Devolucion 5009109080</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Devolucion 5009114474 </t>
+          <t>Devolucion 5009114474</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> nan </t>
+          <t xml:space="preserve"> nan</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> nan </t>
+          <t xml:space="preserve"> nan</t>
         </is>
       </c>
     </row>

--- a/app/Archivos/Template/Template_HRC_copi.xlsx
+++ b/app/Archivos/Template/Template_HRC_copi.xlsx
@@ -528,17 +528,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-914268823.4</v>
+        <v>-1951693656.12</v>
       </c>
     </row>
     <row r="8">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-914268823.4</v>
+        <v>-1951693656.12</v>
       </c>
     </row>
     <row r="9"/>
@@ -700,2193 +700,2785 @@
     <row r="19">
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>PMP1276670</t>
+          <t>PMP1273112</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-4956</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>27974992</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>-4956</v>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1276670</t>
-        </is>
-      </c>
+        <v>27974992</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>PMP1276992</t>
+          <t>PMP1273596</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-4956</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>28749643</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>-4956</v>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1276992</t>
-        </is>
-      </c>
+        <v>28749643</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>PMP1276671</t>
+          <t>PMP1273863</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-128471</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>11408205</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="6" t="n">
-        <v>-128471</v>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1276671</t>
-        </is>
-      </c>
+        <v>11408205</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>PMP1277137</t>
+          <t>PMP1273878</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>-973783</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>154734955</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="6" t="n">
-        <v>-973783</v>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1277137</t>
-        </is>
-      </c>
+        <v>154734955</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PMP1276991</t>
+          <t>PMP1273878</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>-375295</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>-375295</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276991</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>PMP1273112</t>
+          <t>PMP1276666</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>-98733</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>64246828</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
       <c r="H24" s="6" t="n">
-        <v>-98733</v>
-      </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1273112</t>
-        </is>
-      </c>
+        <v>64246828</v>
+      </c>
+      <c r="I24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>PMP1273878</t>
+          <t>PMP1276668</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-1267188</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>65729254</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="6" t="n">
-        <v>-1267188</v>
-      </c>
-      <c r="I25" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1273878</t>
-        </is>
-      </c>
+        <v>65729254</v>
+      </c>
+      <c r="I25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>PMP1276666</t>
+          <t>PMP1276668</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-116211</v>
+        <v>0.6599999964237213</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-116211</v>
+        <v>0.6599999964237213</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276666</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>PMP1276668</t>
+          <t>PMP1276669</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-338713</v>
-      </c>
-      <c r="F27" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G27" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>18919275</v>
+      </c>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="6" t="n">
-        <v>-338713</v>
-      </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1276668</t>
-        </is>
-      </c>
+        <v>18919275</v>
+      </c>
+      <c r="I27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>PMP1276990</t>
+          <t>PMP1276669</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>-538091</v>
+        <v>1.96000000089407</v>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-538091</v>
+        <v>1.96000000089407</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276990</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>PMP1277143</t>
+          <t>PMP1276670</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>-18833393</v>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>8387269</v>
+      </c>
+      <c r="F29" s="10" t="inlineStr"/>
+      <c r="G29" s="10" t="inlineStr"/>
       <c r="H29" s="6" t="n">
-        <v>-18833393</v>
-      </c>
-      <c r="I29" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1277143</t>
-        </is>
-      </c>
+        <v>8387269</v>
+      </c>
+      <c r="I29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>PMP1277142</t>
+          <t>PMP1276670</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>-1272672</v>
+        <v>2.71999999973923</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-1272672</v>
+        <v>2.71999999973923</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1277142</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>PMP1276988</t>
+          <t>PMP1276671</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-182382</v>
-      </c>
-      <c r="F31" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G31" s="10" t="inlineStr">
-        <is>
-          <t>987</t>
-        </is>
-      </c>
+        <v>23118825</v>
+      </c>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
       <c r="H31" s="6" t="n">
-        <v>-182382</v>
-      </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>Reduc Factura Compra PMP1276988</t>
-        </is>
-      </c>
+        <v>23118825</v>
+      </c>
+      <c r="I31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>1200012947</t>
+          <t>PMP1276671</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-143145262</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr"/>
+        <v>0.5399999991059303</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-143145262</v>
+        <v>0.5399999991059303</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>1200013005</t>
+          <t>PMP1276672</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-388554179</v>
+        <v>223440</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
-      <c r="G33" s="10" t="inlineStr">
-        <is>
-          <t>NRO</t>
-        </is>
-      </c>
+      <c r="G33" s="10" t="inlineStr"/>
       <c r="H33" s="6" t="n">
-        <v>-388554179</v>
-      </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
-        </is>
-      </c>
+        <v>223440</v>
+      </c>
+      <c r="I33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>1200013286</t>
+          <t>PMP1276672</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>-795603394</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr"/>
+        <v>0.07999999998719431</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>-795603394</v>
+        <v>0.07999999998719431</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>1200013299</t>
+          <t>PMP1276673</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>-193603927</v>
+        <v>2457840</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>NRO</t>
-        </is>
-      </c>
+      <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="6" t="n">
-        <v>-193603927</v>
-      </c>
-      <c r="I35" s="11" t="inlineStr">
-        <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
-        </is>
-      </c>
+        <v>2457840</v>
+      </c>
+      <c r="I35" s="11" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>1200013300</t>
+          <t>PMP1276988</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>-27876259</v>
+        <v>111183834</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
-      <c r="G36" s="10" t="inlineStr">
-        <is>
-          <t>NRO</t>
-        </is>
-      </c>
+      <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="6" t="n">
-        <v>-27876259</v>
-      </c>
-      <c r="I36" s="11" t="inlineStr">
-        <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
-        </is>
-      </c>
+        <v>111183834</v>
+      </c>
+      <c r="I36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>1200013530</t>
+          <t>PMP1276988</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-504563336</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr"/>
+        <v>3.680000007152557</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
       <c r="G37" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-504563336</v>
+        <v>3.680000007152557</v>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>1200013676</t>
+          <t>PMP1276990</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-12114607</v>
+        <v>91703429</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
-      <c r="G38" s="10" t="inlineStr">
-        <is>
-          <t>NRO</t>
-        </is>
-      </c>
+      <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="6" t="n">
-        <v>-12114607</v>
-      </c>
-      <c r="I38" s="11" t="inlineStr">
-        <is>
-          <t>favor del cliente sin aplicar por falta de soporte</t>
-        </is>
-      </c>
+        <v>91703429</v>
+      </c>
+      <c r="I38" s="11" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>1200013677</t>
+          <t>PMP1276991</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>-903316691</v>
+        <v>21513304</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>NRO</t>
-        </is>
-      </c>
+      <c r="G39" s="10" t="inlineStr"/>
       <c r="H39" s="6" t="n">
-        <v>-903316691</v>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>favor del cliente sin aplicar por falta de soporte</t>
-        </is>
-      </c>
+        <v>21513304</v>
+      </c>
+      <c r="I39" s="11" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>PMP1276992</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>-110942</v>
-      </c>
-      <c r="F40" s="10" t="inlineStr">
-        <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G40" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+        <v>19850219</v>
+      </c>
+      <c r="F40" s="10" t="inlineStr"/>
+      <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="6" t="n">
-        <v>-110942</v>
-      </c>
-      <c r="I40" s="11" t="inlineStr">
-        <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
-        </is>
-      </c>
+        <v>19850219</v>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>PMP1276992</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>-97776</v>
+        <v>1.120000001043081</v>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>-97776</v>
+        <v>1.120000001043081</v>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>PMP1276993</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>-1059035</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G42" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
+        <v>24310076</v>
+      </c>
+      <c r="F42" s="10" t="inlineStr"/>
+      <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="6" t="n">
-        <v>-1059035</v>
-      </c>
-      <c r="I42" s="11" t="inlineStr">
-        <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
-        </is>
-      </c>
+        <v>24310076</v>
+      </c>
+      <c r="I42" s="11" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>PMP1276993</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-481837</v>
+        <v>0.1200000010430813</v>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-481837</v>
+        <v>0.1200000010430813</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277137</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-15664649</v>
-      </c>
-      <c r="F44" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G44" s="10" t="n">
-        <v>987</v>
-      </c>
+        <v>111539485</v>
+      </c>
+      <c r="F44" s="10" t="inlineStr"/>
+      <c r="G44" s="10" t="inlineStr"/>
       <c r="H44" s="6" t="n">
-        <v>-15664649</v>
-      </c>
-      <c r="I44" s="11" t="inlineStr">
-        <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
-        </is>
-      </c>
+        <v>111539485</v>
+      </c>
+      <c r="I44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277137</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-23148793</v>
+        <v>0.1200000047683716</v>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="n">
-        <v>987</v>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-23148793</v>
+        <v>0.1200000047683716</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277138</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>-136694904</v>
-      </c>
-      <c r="F46" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G46" s="10" t="n">
-        <v>987</v>
-      </c>
+        <v>25908600</v>
+      </c>
+      <c r="F46" s="10" t="inlineStr"/>
+      <c r="G46" s="10" t="inlineStr"/>
       <c r="H46" s="6" t="n">
-        <v>-136694904</v>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
-        </is>
-      </c>
+        <v>25908600</v>
+      </c>
+      <c r="I46" s="11" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277139</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>-58852874</v>
-      </c>
-      <c r="F47" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G47" s="10" t="n">
-        <v>987</v>
-      </c>
+        <v>20008459</v>
+      </c>
+      <c r="F47" s="10" t="inlineStr"/>
+      <c r="G47" s="10" t="inlineStr"/>
       <c r="H47" s="6" t="n">
-        <v>-58852874</v>
-      </c>
-      <c r="I47" s="11" t="inlineStr">
-        <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
-        </is>
-      </c>
+        <v>20008459</v>
+      </c>
+      <c r="I47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277139</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>-25771569</v>
+        <v>0.6799999997019768</v>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="n">
-        <v>987</v>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-25771569</v>
+        <v>0.6799999997019768</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PMP1277142</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>-82067413</v>
-      </c>
-      <c r="F49" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="n">
-        <v>987</v>
-      </c>
+        <v>334587580</v>
+      </c>
+      <c r="F49" s="10" t="inlineStr"/>
+      <c r="G49" s="10" t="inlineStr"/>
       <c r="H49" s="6" t="n">
-        <v>-82067413</v>
-      </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>DDPD UNILEVER MIN 2Q 2025</t>
-        </is>
-      </c>
+        <v>334587580</v>
+      </c>
+      <c r="I49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277142</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>-28813</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="n">
-        <v>987</v>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-28813</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277143</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>-3659996</v>
-      </c>
-      <c r="F51" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G51" s="10" t="n">
-        <v>987</v>
-      </c>
+        <v>357532623</v>
+      </c>
+      <c r="F51" s="10" t="inlineStr"/>
+      <c r="G51" s="10" t="inlineStr"/>
       <c r="H51" s="6" t="n">
-        <v>-3659996</v>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
-        </is>
-      </c>
+        <v>357532623</v>
+      </c>
+      <c r="I51" s="11" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277144</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>-1074320</v>
-      </c>
-      <c r="F52" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G52" s="10" t="n">
-        <v>987</v>
-      </c>
+        <v>19509586</v>
+      </c>
+      <c r="F52" s="10" t="inlineStr"/>
+      <c r="G52" s="10" t="inlineStr"/>
       <c r="H52" s="6" t="n">
-        <v>-1074320</v>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
-        </is>
-      </c>
+        <v>19509586</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277144</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>-8010033</v>
+        <v>371.5</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="n">
-        <v>987</v>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>-8010033</v>
+        <v>371.5</v>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277145</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>-209929</v>
-      </c>
-      <c r="F54" s="10" t="inlineStr">
-        <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G54" s="10" t="n">
-        <v>987</v>
-      </c>
+        <v>11842275</v>
+      </c>
+      <c r="F54" s="10" t="inlineStr"/>
+      <c r="G54" s="10" t="inlineStr"/>
       <c r="H54" s="6" t="n">
-        <v>-209929</v>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
-        </is>
-      </c>
+        <v>11842275</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277145</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>-52023765</v>
+        <v>46.24000000022352</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G55" s="10" t="n">
-        <v>987</v>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>-52023765</v>
+        <v>46.24000000022352</v>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200012947</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>-9458910</v>
+        <v>-143145262</v>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr"/>
       <c r="H56" s="6" t="n">
-        <v>-9458910</v>
+        <v>-143145262</v>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Pendiente de Aplicar sin Soporte</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200013005</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>-5923198</v>
+        <v>-388554179</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr"/>
       <c r="H57" s="6" t="n">
-        <v>-5923198</v>
+        <v>-388554179</v>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Pendiente de Aplicar sin Soporte</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200013286</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>-6652327</v>
+        <v>-795603394</v>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr"/>
       <c r="H58" s="6" t="n">
-        <v>-6652327</v>
+        <v>-795603394</v>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Pendiente de Aplicar sin Soporte</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200013299</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>-14421092</v>
+        <v>-193603927</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr"/>
       <c r="H59" s="6" t="n">
-        <v>-14421092</v>
+        <v>-193603927</v>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Pendiente de Aplicar sin Soporte</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200013300</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>-6022678</v>
+        <v>-27876259</v>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr"/>
       <c r="H60" s="6" t="n">
-        <v>-6022678</v>
+        <v>-27876259</v>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Pendiente de Aplicar sin Soporte</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200013530</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>-7052198</v>
+        <v>-504563336</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr"/>
       <c r="H61" s="6" t="n">
-        <v>-7052198</v>
+        <v>-504563336</v>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Pendiente de Aplicar sin Soporte</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200013676</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>-22568987</v>
+        <v>-12114607</v>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr"/>
       <c r="H62" s="6" t="n">
-        <v>-22568987</v>
+        <v>-12114607</v>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>favor del cliente sin aplicar por falta de soporte</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>1200013677</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>-8073343</v>
+        <v>-903316691</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="n">
-        <v>987</v>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr"/>
       <c r="H63" s="6" t="n">
-        <v>-8073343</v>
+        <v>-903316691</v>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>favor del cliente sin aplicar por falta de soporte</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Devolucion</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>5009108214</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-3057002</v>
+        <v>-2743</v>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="n">
-        <v>987</v>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
       </c>
       <c r="H64" s="6" t="n">
-        <v>-3057002</v>
+        <v>-2743</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Devolucion 5009108214</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Devolucion</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>C. UNILEVER</t>
+          <t>5009109080</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>-22013501</v>
+        <v>-13069</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>DPP NO PROCEDE</t>
+          <t>AVERIA</t>
         </is>
       </c>
       <c r="G65" s="10" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>-22013501</v>
+        <v>-13069</v>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</t>
+          <t>Devolucion 5009109080</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Devolucion</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>PMP1276670</t>
+          <t>5009114474</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>8387269</v>
-      </c>
-      <c r="F66" s="10" t="inlineStr"/>
-      <c r="G66" s="10" t="inlineStr"/>
+        <v>-5876</v>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H66" s="6" t="n">
-        <v>8387269</v>
+        <v>-5876</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276670</t>
+          <t>Devolucion 5009114474</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>PMP1277139</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>20008459</v>
-      </c>
-      <c r="F67" s="10" t="inlineStr"/>
-      <c r="G67" s="10" t="inlineStr"/>
+        <v>-110942</v>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H67" s="6" t="n">
-        <v>20008459</v>
+        <v>-110942</v>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277139</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>PMP1276992</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>19850219</v>
-      </c>
-      <c r="F68" s="10" t="inlineStr"/>
-      <c r="G68" s="10" t="inlineStr"/>
+        <v>-97776</v>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H68" s="6" t="n">
-        <v>19850219</v>
+        <v>-97776</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276992</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>PMP1276671</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>23118825</v>
-      </c>
-      <c r="F69" s="10" t="inlineStr"/>
-      <c r="G69" s="10" t="inlineStr"/>
+        <v>-1059035</v>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H69" s="6" t="n">
-        <v>23118825</v>
+        <v>-1059035</v>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276671</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>PMP1276991</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>21513304</v>
-      </c>
-      <c r="F70" s="10" t="inlineStr"/>
-      <c r="G70" s="10" t="inlineStr"/>
+        <v>-481837</v>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
       <c r="H70" s="6" t="n">
-        <v>21513304</v>
+        <v>-481837</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276991</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>PMP1277137</t>
+          <t>C. UNILEVER</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>111539485</v>
-      </c>
-      <c r="F71" s="10" t="inlineStr"/>
-      <c r="G71" s="10" t="inlineStr"/>
+        <v>-22013501</v>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>DPP NO PROCEDE</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
       <c r="H71" s="6" t="n">
-        <v>111539485</v>
+        <v>-22013501</v>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277137</t>
+          <t>DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>PMP1273112</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>27974992</v>
-      </c>
-      <c r="F72" s="10" t="inlineStr"/>
-      <c r="G72" s="10" t="inlineStr"/>
+        <v>-15664649</v>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H72" s="6" t="n">
-        <v>27974992</v>
+        <v>-15664649</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1273112</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>PMP1273596</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>28749643</v>
-      </c>
-      <c r="F73" s="10" t="inlineStr"/>
-      <c r="G73" s="10" t="inlineStr"/>
+        <v>-23148793</v>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H73" s="6" t="n">
-        <v>28749643</v>
+        <v>-23148793</v>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1273596</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>PMP1273863</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>11408205</v>
-      </c>
-      <c r="F74" s="10" t="inlineStr"/>
-      <c r="G74" s="10" t="inlineStr"/>
+        <v>-136694904</v>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H74" s="6" t="n">
-        <v>11408205</v>
+        <v>-136694904</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1273863</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>PMP1273878</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>154734955</v>
-      </c>
-      <c r="F75" s="10" t="inlineStr"/>
-      <c r="G75" s="10" t="inlineStr"/>
+        <v>-58852874</v>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H75" s="6" t="n">
-        <v>154734955</v>
+        <v>-58852874</v>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1273878</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>PMP1276669</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>18919275</v>
-      </c>
-      <c r="F76" s="10" t="inlineStr"/>
-      <c r="G76" s="10" t="inlineStr"/>
+        <v>-25771569</v>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H76" s="6" t="n">
-        <v>18919275</v>
+        <v>-25771569</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276669</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>PMP1277138</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>25908600</v>
-      </c>
-      <c r="F77" s="10" t="inlineStr"/>
-      <c r="G77" s="10" t="inlineStr"/>
+        <v>-28813</v>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H77" s="6" t="n">
-        <v>25908600</v>
+        <v>-28813</v>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277138</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>PMP1276993</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>24310076</v>
-      </c>
-      <c r="F78" s="10" t="inlineStr"/>
-      <c r="G78" s="10" t="inlineStr"/>
+        <v>-3659996</v>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H78" s="6" t="n">
-        <v>24310076</v>
+        <v>-3659996</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276993</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>PMP1276666</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>64246828</v>
-      </c>
-      <c r="F79" s="10" t="inlineStr"/>
-      <c r="G79" s="10" t="inlineStr"/>
+        <v>-1074320</v>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H79" s="6" t="n">
-        <v>64246828</v>
+        <v>-1074320</v>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276666</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>PMP1276672</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>223440</v>
-      </c>
-      <c r="F80" s="10" t="inlineStr"/>
-      <c r="G80" s="10" t="inlineStr"/>
+        <v>-8010033</v>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H80" s="6" t="n">
-        <v>223440</v>
+        <v>-8010033</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276672</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>PMP1276673</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>2457840</v>
-      </c>
-      <c r="F81" s="10" t="inlineStr"/>
-      <c r="G81" s="10" t="inlineStr"/>
+        <v>-209929</v>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H81" s="6" t="n">
-        <v>2457840</v>
+        <v>-209929</v>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276673</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>PMP1276668</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>65729254</v>
-      </c>
-      <c r="F82" s="10" t="inlineStr"/>
-      <c r="G82" s="10" t="inlineStr"/>
+        <v>-52023765</v>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H82" s="6" t="n">
-        <v>65729254</v>
+        <v>-52023765</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276668</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>PMP1277145</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>11842275</v>
-      </c>
-      <c r="F83" s="10" t="inlineStr"/>
-      <c r="G83" s="10" t="inlineStr"/>
+        <v>-9458910</v>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H83" s="6" t="n">
-        <v>11842275</v>
+        <v>-9458910</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277145</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>PMP1277144</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>19509586</v>
-      </c>
-      <c r="F84" s="10" t="inlineStr"/>
-      <c r="G84" s="10" t="inlineStr"/>
+        <v>-5923198</v>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H84" s="6" t="n">
-        <v>19509586</v>
+        <v>-5923198</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277144</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>PMP1276990</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E85" s="6" t="n">
-        <v>91703429</v>
-      </c>
-      <c r="F85" s="10" t="inlineStr"/>
-      <c r="G85" s="10" t="inlineStr"/>
+        <v>-6652327</v>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H85" s="6" t="n">
-        <v>91703429</v>
+        <v>-6652327</v>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276990</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>PMP1277143</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>357532623</v>
-      </c>
-      <c r="F86" s="10" t="inlineStr"/>
-      <c r="G86" s="10" t="inlineStr"/>
+        <v>-14421092</v>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H86" s="6" t="n">
-        <v>357532623</v>
+        <v>-14421092</v>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277143</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>PMP1277142</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>334587580</v>
-      </c>
-      <c r="F87" s="10" t="inlineStr"/>
-      <c r="G87" s="10" t="inlineStr"/>
+        <v>-6022678</v>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H87" s="6" t="n">
-        <v>334587580</v>
+        <v>-6022678</v>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1277142</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Factura Acrededor</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>PMP1276988</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>111183834</v>
-      </c>
-      <c r="F88" s="10" t="inlineStr"/>
-      <c r="G88" s="10" t="inlineStr"/>
+        <v>-7052198</v>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H88" s="6" t="n">
-        <v>111183834</v>
+        <v>-7052198</v>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>Factura Acrededor PMP1276988</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Devolucion</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>5009108214</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>-2743</v>
+        <v>-22568987</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H89" s="6" t="n">
-        <v>-2743</v>
+        <v>-22568987</v>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>Devolucion 5009108214</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Devolucion</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>5009109080</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>-13069</v>
+        <v>-8073343</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G90" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H90" s="6" t="n">
-        <v>-13069</v>
+        <v>-8073343</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>Devolucion 5009109080</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Devolucion</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>5009114474</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E91" s="6" t="n">
-        <v>-5876</v>
+        <v>-3057002</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G91" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H91" s="6" t="n">
-        <v>-5876</v>
+        <v>-3057002</v>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>Devolucion 5009114474</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="C92" s="10" t="inlineStr"/>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
+          <t>PMP1273112</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n">
+        <v>-98733</v>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="n">
+        <v>-98733</v>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1273112</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>PMP1273112</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n">
+        <v>-2.120000001043081</v>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="n">
+        <v>-2.120000001043081</v>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>PMP1273596</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n">
+        <v>-0.8000000007450581</v>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="n">
+        <v>-0.8000000007450581</v>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>PMP1273863</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="n">
+        <v>-1.96000000089407</v>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="n">
+        <v>-1.96000000089407</v>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>PMP1273878</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n">
+        <v>-1267188</v>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="n">
+        <v>-1267188</v>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1273878</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276666</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="n">
+        <v>-116211</v>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="n">
+        <v>-116211</v>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276666</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276666</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n">
+        <v>-0.7800000011920929</v>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="n">
+        <v>-0.7800000011920929</v>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276668</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="n">
+        <v>-338713</v>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n">
+        <v>-338713</v>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276668</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276670</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n">
+        <v>-4956</v>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="n">
+        <v>-4956</v>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276670</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276671</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="n">
+        <v>-128471</v>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="n">
+        <v>-128471</v>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276671</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276673</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n">
+        <v>-0.1200000001117587</v>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="n">
+        <v>-0.1200000001117587</v>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276988</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="n">
+        <v>-182382</v>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="n">
+        <v>-182382</v>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276988</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276990</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="n">
+        <v>-538091</v>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="n">
+        <v>-538091</v>
+      </c>
+      <c r="I104" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276990</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276990</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="n">
+        <v>-3.459999993443489</v>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="n">
+        <v>-3.459999993443489</v>
+      </c>
+      <c r="I105" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276991</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="n">
+        <v>-375295</v>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="n">
+        <v>-375295</v>
+      </c>
+      <c r="I106" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276991</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276991</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="n">
+        <v>-1.019999999552965</v>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="n">
+        <v>-1.019999999552965</v>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>PMP1276992</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="n">
+        <v>-4956</v>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="n">
+        <v>-4956</v>
+      </c>
+      <c r="I108" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1276992</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>PMP1277137</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="n">
+        <v>-973783</v>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="n">
+        <v>-973783</v>
+      </c>
+      <c r="I109" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1277137</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>PMP1277142</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="n">
+        <v>-1272672</v>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="n">
+        <v>-1272672</v>
+      </c>
+      <c r="I110" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1277142</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>PMP1277143</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="n">
+        <v>-18833393</v>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G111" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="n">
+        <v>-18833393</v>
+      </c>
+      <c r="I111" s="11" t="inlineStr">
+        <is>
+          <t>Reduc Factura Compra PMP1277143</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="C112" s="10" t="inlineStr">
+        <is>
+          <t>Descuentos no asociados a FC</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>PMP1277143</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="n">
+        <v>-2.060000002384186</v>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="n">
+        <v>-2.060000002384186</v>
+      </c>
+      <c r="I112" s="11" t="inlineStr">
+        <is>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" s="10" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n">
-        <v>1017083580</v>
-      </c>
-      <c r="F92" s="10" t="inlineStr"/>
-      <c r="G92" s="10" t="inlineStr"/>
-      <c r="H92" s="6" t="n">
-        <v>1017083580</v>
-      </c>
-      <c r="I92" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="C93" s="10" t="inlineStr"/>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="n">
-        <v>20341671.6</v>
-      </c>
-      <c r="F93" s="10" t="inlineStr"/>
-      <c r="G93" s="10" t="inlineStr"/>
-      <c r="H93" s="6" t="n">
-        <v>20341671.6</v>
-      </c>
-      <c r="I93" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> nan</t>
+      <c r="E113" s="6" t="n">
+        <v>-82067413</v>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="n">
+        <v>987</v>
+      </c>
+      <c r="H113" s="6" t="n">
+        <v>-82067413</v>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>DDPD UNILEVER MIN 2Q 2025</t>
         </is>
       </c>
     </row>

--- a/app/Archivos/Template/Template_HRC_copi.xlsx
+++ b/app/Archivos/Template/Template_HRC_copi.xlsx
@@ -700,192 +700,232 @@
     <row r="19">
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>PMP1273112</t>
+          <t>1200012947</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>27974992</v>
-      </c>
-      <c r="F19" s="10" t="inlineStr"/>
+        <v>-143145262</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>NRO</t>
+        </is>
+      </c>
       <c r="G19" s="10" t="inlineStr"/>
       <c r="H19" s="6" t="n">
-        <v>27974992</v>
-      </c>
-      <c r="I19" s="11" t="inlineStr"/>
+        <v>-143145262</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Pendiente de Aplicar sin Soporte</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>PMP1273596</t>
+          <t>1200013005</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>28749643</v>
-      </c>
-      <c r="F20" s="10" t="inlineStr"/>
+        <v>-388554179</v>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>NRO</t>
+        </is>
+      </c>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="6" t="n">
-        <v>28749643</v>
-      </c>
-      <c r="I20" s="11" t="inlineStr"/>
+        <v>-388554179</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Pendiente de Aplicar sin Soporte</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>PMP1273863</t>
+          <t>1200013286</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>11408205</v>
-      </c>
-      <c r="F21" s="10" t="inlineStr"/>
+        <v>-795603394</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>NRO</t>
+        </is>
+      </c>
       <c r="G21" s="10" t="inlineStr"/>
       <c r="H21" s="6" t="n">
-        <v>11408205</v>
-      </c>
-      <c r="I21" s="11" t="inlineStr"/>
+        <v>-795603394</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Pendiente de Aplicar sin Soporte</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>PMP1273878</t>
+          <t>1200013299</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>154734955</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr"/>
+        <v>-193603927</v>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>NRO</t>
+        </is>
+      </c>
       <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="6" t="n">
-        <v>154734955</v>
-      </c>
-      <c r="I22" s="11" t="inlineStr"/>
+        <v>-193603927</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Pendiente de Aplicar sin Soporte</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>PMP1273878</t>
+          <t>1200013300</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.6800000071525574</v>
+        <v>-27876259</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr"/>
       <c r="H23" s="6" t="n">
-        <v>0.6800000071525574</v>
+        <v>-27876259</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>Pendiente de Aplicar sin Soporte</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>PMP1276666</t>
+          <t>1200013530</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>64246828</v>
-      </c>
-      <c r="F24" s="10" t="inlineStr"/>
+        <v>-504563336</v>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>NRO</t>
+        </is>
+      </c>
       <c r="G24" s="10" t="inlineStr"/>
       <c r="H24" s="6" t="n">
-        <v>64246828</v>
-      </c>
-      <c r="I24" s="11" t="inlineStr"/>
+        <v>-504563336</v>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>Pendiente de Aplicar sin Soporte</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>PMP1276668</t>
+          <t>1200013676</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>65729254</v>
-      </c>
-      <c r="F25" s="10" t="inlineStr"/>
+        <v>-12114607</v>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>NRO</t>
+        </is>
+      </c>
       <c r="G25" s="10" t="inlineStr"/>
       <c r="H25" s="6" t="n">
-        <v>65729254</v>
-      </c>
-      <c r="I25" s="11" t="inlineStr"/>
+        <v>-12114607</v>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>favor del cliente sin aplicar por falta de soporte</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Nota de Crédito</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>PMP1276668</t>
+          <t>1200013677</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.6599999964237213</v>
+        <v>-903316691</v>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+          <t>NRO</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="6" t="n">
-        <v>0.6599999964237213</v>
+        <v>-903316691</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>favor del cliente sin aplicar por falta de soporte</t>
         </is>
       </c>
     </row>
@@ -897,51 +937,39 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>PMP1276669</t>
+          <t>PMP1273112</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>18919275</v>
+        <v>27974992</v>
       </c>
       <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr"/>
       <c r="H27" s="6" t="n">
-        <v>18919275</v>
+        <v>27974992</v>
       </c>
       <c r="I27" s="11" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>PMP1276669</t>
+          <t>PMP1273596</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1.96000000089407</v>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>28749643</v>
+      </c>
+      <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="10" t="inlineStr"/>
       <c r="H28" s="6" t="n">
-        <v>1.96000000089407</v>
-      </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>28749643</v>
+      </c>
+      <c r="I28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="C29" s="10" t="inlineStr">
@@ -951,51 +979,39 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>PMP1276670</t>
+          <t>PMP1273863</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>8387269</v>
+        <v>11408205</v>
       </c>
       <c r="F29" s="10" t="inlineStr"/>
       <c r="G29" s="10" t="inlineStr"/>
       <c r="H29" s="6" t="n">
-        <v>8387269</v>
+        <v>11408205</v>
       </c>
       <c r="I29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>PMP1276670</t>
+          <t>PMP1273878</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2.71999999973923</v>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>154734955</v>
+      </c>
+      <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr"/>
       <c r="H30" s="6" t="n">
-        <v>2.71999999973923</v>
-      </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>154734955</v>
+      </c>
+      <c r="I30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="C31" s="10" t="inlineStr">
@@ -1005,51 +1021,39 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>PMP1276671</t>
+          <t>PMP1276666</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>23118825</v>
+        <v>64246828</v>
       </c>
       <c r="F31" s="10" t="inlineStr"/>
       <c r="G31" s="10" t="inlineStr"/>
       <c r="H31" s="6" t="n">
-        <v>23118825</v>
+        <v>64246828</v>
       </c>
       <c r="I31" s="11" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>PMP1276671</t>
+          <t>PMP1276668</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.5399999991059303</v>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>65729254</v>
+      </c>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
       <c r="H32" s="6" t="n">
-        <v>0.5399999991059303</v>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>65729254</v>
+      </c>
+      <c r="I32" s="11" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="C33" s="10" t="inlineStr">
@@ -1059,51 +1063,39 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>PMP1276672</t>
+          <t>PMP1276669</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>223440</v>
+        <v>18919275</v>
       </c>
       <c r="F33" s="10" t="inlineStr"/>
       <c r="G33" s="10" t="inlineStr"/>
       <c r="H33" s="6" t="n">
-        <v>223440</v>
+        <v>18919275</v>
       </c>
       <c r="I33" s="11" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>PMP1276672</t>
+          <t>PMP1276670</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.07999999998719431</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>8387269</v>
+      </c>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr"/>
       <c r="H34" s="6" t="n">
-        <v>0.07999999998719431</v>
-      </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>8387269</v>
+      </c>
+      <c r="I34" s="11" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="C35" s="10" t="inlineStr">
@@ -1113,16 +1105,16 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>PMP1276673</t>
+          <t>PMP1276671</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>2457840</v>
+        <v>23118825</v>
       </c>
       <c r="F35" s="10" t="inlineStr"/>
       <c r="G35" s="10" t="inlineStr"/>
       <c r="H35" s="6" t="n">
-        <v>2457840</v>
+        <v>23118825</v>
       </c>
       <c r="I35" s="11" t="inlineStr"/>
     </row>
@@ -1134,51 +1126,39 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>PMP1276988</t>
+          <t>PMP1276672</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>111183834</v>
+        <v>223440</v>
       </c>
       <c r="F36" s="10" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="6" t="n">
-        <v>111183834</v>
+        <v>223440</v>
       </c>
       <c r="I36" s="11" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>PMP1276988</t>
+          <t>PMP1276673</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>3.680000007152557</v>
-      </c>
-      <c r="F37" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G37" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>2457840</v>
+      </c>
+      <c r="F37" s="10" t="inlineStr"/>
+      <c r="G37" s="10" t="inlineStr"/>
       <c r="H37" s="6" t="n">
-        <v>3.680000007152557</v>
-      </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>2457840</v>
+      </c>
+      <c r="I37" s="11" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="C38" s="10" t="inlineStr">
@@ -1188,16 +1168,16 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>PMP1276990</t>
+          <t>PMP1276988</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>91703429</v>
+        <v>111183834</v>
       </c>
       <c r="F38" s="10" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="6" t="n">
-        <v>91703429</v>
+        <v>111183834</v>
       </c>
       <c r="I38" s="11" t="inlineStr"/>
     </row>
@@ -1209,16 +1189,16 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>PMP1276991</t>
+          <t>PMP1276990</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>21513304</v>
+        <v>91703429</v>
       </c>
       <c r="F39" s="10" t="inlineStr"/>
       <c r="G39" s="10" t="inlineStr"/>
       <c r="H39" s="6" t="n">
-        <v>21513304</v>
+        <v>91703429</v>
       </c>
       <c r="I39" s="11" t="inlineStr"/>
     </row>
@@ -1230,23 +1210,23 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>PMP1276992</t>
+          <t>PMP1276991</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>19850219</v>
+        <v>21513304</v>
       </c>
       <c r="F40" s="10" t="inlineStr"/>
       <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="6" t="n">
-        <v>19850219</v>
+        <v>21513304</v>
       </c>
       <c r="I40" s="11" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
@@ -1255,26 +1235,14 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>1.120000001043081</v>
-      </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>19850219</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr"/>
+      <c r="G41" s="10" t="inlineStr"/>
       <c r="H41" s="6" t="n">
-        <v>1.120000001043081</v>
-      </c>
-      <c r="I41" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>19850219</v>
+      </c>
+      <c r="I41" s="11" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="C42" s="10" t="inlineStr">
@@ -1300,35 +1268,23 @@
     <row r="43">
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>PMP1276993</t>
+          <t>PMP1277137</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.1200000010430813</v>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>111539485</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr"/>
+      <c r="G43" s="10" t="inlineStr"/>
       <c r="H43" s="6" t="n">
-        <v>0.1200000010430813</v>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>111539485</v>
+      </c>
+      <c r="I43" s="11" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="C44" s="10" t="inlineStr">
@@ -1338,51 +1294,39 @@
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>PMP1277137</t>
+          <t>PMP1277138</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>111539485</v>
+        <v>25908600</v>
       </c>
       <c r="F44" s="10" t="inlineStr"/>
       <c r="G44" s="10" t="inlineStr"/>
       <c r="H44" s="6" t="n">
-        <v>111539485</v>
+        <v>25908600</v>
       </c>
       <c r="I44" s="11" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>PMP1277137</t>
+          <t>PMP1277139</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.1200000047683716</v>
-      </c>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G45" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>20008459</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr"/>
+      <c r="G45" s="10" t="inlineStr"/>
       <c r="H45" s="6" t="n">
-        <v>0.1200000047683716</v>
-      </c>
-      <c r="I45" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>20008459</v>
+      </c>
+      <c r="I45" s="11" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="C46" s="10" t="inlineStr">
@@ -1392,16 +1336,16 @@
       </c>
       <c r="D46" s="10" t="inlineStr">
         <is>
-          <t>PMP1277138</t>
+          <t>PMP1277142</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>25908600</v>
+        <v>334587580</v>
       </c>
       <c r="F46" s="10" t="inlineStr"/>
       <c r="G46" s="10" t="inlineStr"/>
       <c r="H46" s="6" t="n">
-        <v>25908600</v>
+        <v>334587580</v>
       </c>
       <c r="I46" s="11" t="inlineStr"/>
     </row>
@@ -1413,51 +1357,39 @@
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>PMP1277139</t>
+          <t>PMP1277143</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>20008459</v>
+        <v>357532623</v>
       </c>
       <c r="F47" s="10" t="inlineStr"/>
       <c r="G47" s="10" t="inlineStr"/>
       <c r="H47" s="6" t="n">
-        <v>20008459</v>
+        <v>357532623</v>
       </c>
       <c r="I47" s="11" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Factura</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>PMP1277139</t>
+          <t>PMP1277144</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.6799999997019768</v>
-      </c>
-      <c r="F48" s="10" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G48" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
+        <v>19509586</v>
+      </c>
+      <c r="F48" s="10" t="inlineStr"/>
+      <c r="G48" s="10" t="inlineStr"/>
       <c r="H48" s="6" t="n">
-        <v>0.6799999997019768</v>
-      </c>
-      <c r="I48" s="11" t="inlineStr">
-        <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
+        <v>19509586</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="C49" s="10" t="inlineStr">
@@ -1467,509 +1399,543 @@
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>PMP1277142</t>
+          <t>PMP1277145</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>334587580</v>
+        <v>11842275</v>
       </c>
       <c r="F49" s="10" t="inlineStr"/>
       <c r="G49" s="10" t="inlineStr"/>
       <c r="H49" s="6" t="n">
-        <v>334587580</v>
+        <v>11842275</v>
       </c>
       <c r="I49" s="11" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>PMP1277142</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>1.100000023841858</v>
+        <v>-15664649</v>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G50" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>1.100000023841858</v>
+        <v>-15664649</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>PMP1277143</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>357532623</v>
-      </c>
-      <c r="F51" s="10" t="inlineStr"/>
-      <c r="G51" s="10" t="inlineStr"/>
+        <v>-23148793</v>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H51" s="6" t="n">
-        <v>357532623</v>
-      </c>
-      <c r="I51" s="11" t="inlineStr"/>
+        <v>-23148793</v>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>PMP1277144</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>19509586</v>
-      </c>
-      <c r="F52" s="10" t="inlineStr"/>
-      <c r="G52" s="10" t="inlineStr"/>
+        <v>-136694904</v>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H52" s="6" t="n">
-        <v>19509586</v>
-      </c>
-      <c r="I52" s="11" t="inlineStr"/>
+        <v>-136694904</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>PMP1277144</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>371.5</v>
+        <v>-58852874</v>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>371.5</v>
+        <v>-58852874</v>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Factura</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>PMP1277145</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>11842275</v>
-      </c>
-      <c r="F54" s="10" t="inlineStr"/>
-      <c r="G54" s="10" t="inlineStr"/>
+        <v>-25771569</v>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H54" s="6" t="n">
-        <v>11842275</v>
-      </c>
-      <c r="I54" s="11" t="inlineStr"/>
+        <v>-25771569</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>Descuentos no asociados a FC</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>PMP1277145</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>46.24000000022352</v>
+        <v>-28813</v>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
-        </is>
-      </c>
-      <c r="G55" s="10" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>46.24000000022352</v>
+        <v>-28813</v>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>MENORES VALORES</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>1200012947</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>-143145262</v>
+        <v>-3659996</v>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G56" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H56" s="6" t="n">
-        <v>-143145262</v>
+        <v>-3659996</v>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>1200013005</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>-388554179</v>
+        <v>-1074320</v>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G57" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H57" s="6" t="n">
-        <v>-388554179</v>
+        <v>-1074320</v>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>1200013286</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>-795603394</v>
+        <v>-8010033</v>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G58" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H58" s="6" t="n">
-        <v>-795603394</v>
+        <v>-8010033</v>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>1200013299</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>-193603927</v>
+        <v>-209929</v>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G59" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H59" s="6" t="n">
-        <v>-193603927</v>
+        <v>-209929</v>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>1200013300</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>-27876259</v>
+        <v>-52023765</v>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G60" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H60" s="6" t="n">
-        <v>-27876259</v>
+        <v>-52023765</v>
       </c>
       <c r="I60" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
         <is>
-          <t>1200013530</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>-504563336</v>
+        <v>-9458910</v>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G61" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H61" s="6" t="n">
-        <v>-504563336</v>
+        <v>-9458910</v>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>Pendiente de Aplicar sin Soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>1200013676</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>-12114607</v>
+        <v>-5923198</v>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G62" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H62" s="6" t="n">
-        <v>-12114607</v>
+        <v>-5923198</v>
       </c>
       <c r="I62" s="11" t="inlineStr">
         <is>
-          <t>favor del cliente sin aplicar por falta de soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Nota de Crédito</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>1200013677</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>-903316691</v>
+        <v>-6652327</v>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>NRO</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="inlineStr"/>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="n">
+        <v>987</v>
+      </c>
       <c r="H63" s="6" t="n">
-        <v>-903316691</v>
+        <v>-6652327</v>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>favor del cliente sin aplicar por falta de soporte</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Devolucion</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>5009108214</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>-2743</v>
+        <v>-14421092</v>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>-2743</v>
+        <v>-14421092</v>
       </c>
       <c r="I64" s="11" t="inlineStr">
         <is>
-          <t>Devolucion 5009108214</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Devolucion</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>5009109080</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>-13069</v>
+        <v>-6022678</v>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H65" s="6" t="n">
-        <v>-13069</v>
+        <v>-6022678</v>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>Devolucion 5009109080</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Devolucion</t>
+          <t>Nota</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>5009114474</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E66" s="6" t="n">
-        <v>-5876</v>
+        <v>-7052198</v>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H66" s="6" t="n">
-        <v>-5876</v>
+        <v>-7052198</v>
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>Devolucion 5009114474</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -1981,28 +1947,26 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
-        <v>-110942</v>
+        <v>-22568987</v>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>-110942</v>
+        <v>-22568987</v>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2014,28 +1978,26 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E68" s="6" t="n">
-        <v>-97776</v>
+        <v>-8073343</v>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H68" s="6" t="n">
-        <v>-97776</v>
+        <v>-8073343</v>
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2047,28 +2009,26 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>NOTA DEVOLUCIÓN</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>-1059035</v>
+        <v>-3057002</v>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G69" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H69" s="6" t="n">
-        <v>-1059035</v>
+        <v>-3057002</v>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
         </is>
       </c>
     </row>
@@ -2080,123 +2040,125 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>AUT.G.COMERCIAL</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="E70" s="6" t="n">
-        <v>-481837</v>
+        <v>-82067413</v>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>AVERIA</t>
-        </is>
-      </c>
-      <c r="G70" s="10" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
+          <t>DESCUENTO</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="n">
+        <v>987</v>
       </c>
       <c r="H70" s="6" t="n">
-        <v>-481837</v>
+        <v>-82067413</v>
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
+          <t>DDPD UNILEVER MIN 2Q 2025</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Devolucion</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>C. UNILEVER</t>
+          <t>5009108214</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
-        <v>-22013501</v>
+        <v>-2743</v>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>DPP NO PROCEDE</t>
+          <t>AVERIA</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>522</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>-22013501</v>
+        <v>-2743</v>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</t>
+          <t>Devolucion 5009108214</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Devolucion</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>5009109080</t>
         </is>
       </c>
       <c r="E72" s="6" t="n">
-        <v>-15664649</v>
+        <v>-13069</v>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G72" s="10" t="n">
-        <v>987</v>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
       </c>
       <c r="H72" s="6" t="n">
-        <v>-15664649</v>
+        <v>-13069</v>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Devolucion 5009109080</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Devolucion</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>5009114474</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>-23148793</v>
+        <v>-5876</v>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="n">
-        <v>987</v>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>-23148793</v>
+        <v>-5876</v>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Devolucion 5009114474</t>
         </is>
       </c>
     </row>
@@ -2208,26 +2170,28 @@
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E74" s="6" t="n">
-        <v>-136694904</v>
+        <v>-110942</v>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="n">
-        <v>987</v>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
       </c>
       <c r="H74" s="6" t="n">
-        <v>-136694904</v>
+        <v>-110942</v>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -2239,26 +2203,28 @@
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
-        <v>-58852874</v>
+        <v>-97776</v>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="n">
-        <v>987</v>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>-58852874</v>
+        <v>-97776</v>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -2270,26 +2236,28 @@
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E76" s="6" t="n">
-        <v>-25771569</v>
+        <v>-1059035</v>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="n">
-        <v>987</v>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
       </c>
       <c r="H76" s="6" t="n">
-        <v>-25771569</v>
+        <v>-1059035</v>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -2301,26 +2269,28 @@
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>AUT.G.COMERCIAL</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
-        <v>-28813</v>
+        <v>-481837</v>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G77" s="10" t="n">
-        <v>987</v>
+          <t>AVERIA</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>-28813</v>
+        <v>-481837</v>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Dev.&gt;.a.30.dias.en.CEDI.8_Sep_</t>
         </is>
       </c>
     </row>
@@ -2332,462 +2302,490 @@
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>C. UNILEVER</t>
         </is>
       </c>
       <c r="E78" s="6" t="n">
-        <v>-3659996</v>
+        <v>-22013501</v>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="n">
-        <v>987</v>
+          <t>DPP NO PROCEDE</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
       </c>
       <c r="H78" s="6" t="n">
-        <v>-3659996</v>
+        <v>-22013501</v>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>DCTO 2.00% GLOBAL PAGO ANTICIPADO UNILEVER</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1273112</t>
         </is>
       </c>
       <c r="E79" s="6" t="n">
-        <v>-1074320</v>
+        <v>-98733</v>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G79" s="10" t="n">
-        <v>987</v>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>-1074320</v>
+        <v>-98733</v>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1273112</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1273878</t>
         </is>
       </c>
       <c r="E80" s="6" t="n">
-        <v>-8010033</v>
+        <v>-1267188</v>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G80" s="10" t="n">
-        <v>987</v>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H80" s="6" t="n">
-        <v>-8010033</v>
+        <v>-1267188</v>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1273878</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276666</t>
         </is>
       </c>
       <c r="E81" s="6" t="n">
-        <v>-209929</v>
+        <v>-116211</v>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G81" s="10" t="n">
-        <v>987</v>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>-209929</v>
+        <v>-116211</v>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276666</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276668</t>
         </is>
       </c>
       <c r="E82" s="6" t="n">
-        <v>-52023765</v>
+        <v>-338713</v>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G82" s="10" t="n">
-        <v>987</v>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H82" s="6" t="n">
-        <v>-52023765</v>
+        <v>-338713</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276668</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276670</t>
         </is>
       </c>
       <c r="E83" s="6" t="n">
-        <v>-9458910</v>
+        <v>-4956</v>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G83" s="10" t="n">
-        <v>987</v>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>-9458910</v>
+        <v>-4956</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276670</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276671</t>
         </is>
       </c>
       <c r="E84" s="6" t="n">
-        <v>-5923198</v>
+        <v>-128471</v>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G84" s="10" t="n">
-        <v>987</v>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H84" s="6" t="n">
-        <v>-5923198</v>
+        <v>-128471</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276671</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276988</t>
         </is>
       </c>
       <c r="E85" s="6" t="n">
-        <v>-6652327</v>
+        <v>-182382</v>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G85" s="10" t="n">
-        <v>987</v>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>-6652327</v>
+        <v>-182382</v>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276988</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276990</t>
         </is>
       </c>
       <c r="E86" s="6" t="n">
-        <v>-14421092</v>
+        <v>-538091</v>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G86" s="10" t="n">
-        <v>987</v>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H86" s="6" t="n">
-        <v>-14421092</v>
+        <v>-538091</v>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276990</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276991</t>
         </is>
       </c>
       <c r="E87" s="6" t="n">
-        <v>-6022678</v>
+        <v>-375295</v>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G87" s="10" t="n">
-        <v>987</v>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>-6022678</v>
+        <v>-375295</v>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276991</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1276992</t>
         </is>
       </c>
       <c r="E88" s="6" t="n">
-        <v>-7052198</v>
+        <v>-4956</v>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G88" s="10" t="n">
-        <v>987</v>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H88" s="6" t="n">
-        <v>-7052198</v>
+        <v>-4956</v>
       </c>
       <c r="I88" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1276992</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277137</t>
         </is>
       </c>
       <c r="E89" s="6" t="n">
-        <v>-22568987</v>
+        <v>-973783</v>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G89" s="10" t="n">
-        <v>987</v>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>-22568987</v>
+        <v>-973783</v>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1277137</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277142</t>
         </is>
       </c>
       <c r="E90" s="6" t="n">
-        <v>-8073343</v>
+        <v>-1272672</v>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G90" s="10" t="n">
-        <v>987</v>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H90" s="6" t="n">
-        <v>-8073343</v>
+        <v>-1272672</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1277142</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Reduc Factura Compra</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN</t>
+          <t>PMP1277143</t>
         </is>
       </c>
       <c r="E91" s="6" t="n">
-        <v>-3057002</v>
+        <v>-18833393</v>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
           <t>DESCUENTO</t>
         </is>
       </c>
-      <c r="G91" s="10" t="n">
-        <v>987</v>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>-3057002</v>
+        <v>-18833393</v>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>NOTA DEVOLUCIÓN POR DEPURACIÓN INVENTARIO SEP 25</t>
+          <t>Reduc Factura Compra PMP1277143</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>PMP1273112</t>
+          <t>PMP1273878</t>
         </is>
       </c>
       <c r="E92" s="6" t="n">
-        <v>-98733</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H92" s="6" t="n">
-        <v>-98733</v>
+        <v>0.6800000071525574</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1273112</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -2799,11 +2797,11 @@
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>PMP1273112</t>
+          <t>PMP1276668</t>
         </is>
       </c>
       <c r="E93" s="6" t="n">
-        <v>-2.120000001043081</v>
+        <v>0.6599999964237213</v>
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
@@ -2812,11 +2810,11 @@
       </c>
       <c r="G93" s="10" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>-2.120000001043081</v>
+        <v>0.6599999964237213</v>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
@@ -2832,11 +2830,11 @@
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>PMP1273596</t>
+          <t>PMP1276669</t>
         </is>
       </c>
       <c r="E94" s="6" t="n">
-        <v>-0.8000000007450581</v>
+        <v>1.96000000089407</v>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
@@ -2845,11 +2843,11 @@
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H94" s="6" t="n">
-        <v>-0.8000000007450581</v>
+        <v>1.96000000089407</v>
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
@@ -2865,11 +2863,11 @@
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>PMP1273863</t>
+          <t>PMP1276670</t>
         </is>
       </c>
       <c r="E95" s="6" t="n">
-        <v>-1.96000000089407</v>
+        <v>2.71999999973923</v>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
@@ -2878,11 +2876,11 @@
       </c>
       <c r="G95" s="10" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>-1.96000000089407</v>
+        <v>2.71999999973923</v>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
@@ -2893,66 +2891,66 @@
     <row r="96">
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>PMP1273878</t>
+          <t>PMP1276671</t>
         </is>
       </c>
       <c r="E96" s="6" t="n">
-        <v>-1267188</v>
+        <v>0.5399999991059303</v>
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H96" s="6" t="n">
-        <v>-1267188</v>
+        <v>0.5399999991059303</v>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1273878</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>PMP1276666</t>
+          <t>PMP1276672</t>
         </is>
       </c>
       <c r="E97" s="6" t="n">
-        <v>-116211</v>
+        <v>0.07999999998719431</v>
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G97" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>-116211</v>
+        <v>0.07999999998719431</v>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276666</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -2964,11 +2962,11 @@
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>PMP1276666</t>
+          <t>PMP1276988</t>
         </is>
       </c>
       <c r="E98" s="6" t="n">
-        <v>-0.7800000011920929</v>
+        <v>3.680000007152557</v>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
@@ -2977,11 +2975,11 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H98" s="6" t="n">
-        <v>-0.7800000011920929</v>
+        <v>3.680000007152557</v>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
@@ -2992,99 +2990,99 @@
     <row r="99">
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>PMP1276668</t>
+          <t>PMP1276992</t>
         </is>
       </c>
       <c r="E99" s="6" t="n">
-        <v>-338713</v>
+        <v>1.120000001043081</v>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G99" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>-338713</v>
+        <v>1.120000001043081</v>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276668</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>PMP1276670</t>
+          <t>PMP1276993</t>
         </is>
       </c>
       <c r="E100" s="6" t="n">
-        <v>-4956</v>
+        <v>0.1200000010430813</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H100" s="6" t="n">
-        <v>-4956</v>
+        <v>0.1200000010430813</v>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276670</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>PMP1276671</t>
+          <t>PMP1277137</t>
         </is>
       </c>
       <c r="E101" s="6" t="n">
-        <v>-128471</v>
+        <v>0.1200000047683716</v>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G101" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>-128471</v>
+        <v>0.1200000047683716</v>
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276671</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -3096,11 +3094,11 @@
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>PMP1276673</t>
+          <t>PMP1277139</t>
         </is>
       </c>
       <c r="E102" s="6" t="n">
-        <v>-0.1200000001117587</v>
+        <v>0.6799999997019768</v>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
@@ -3109,11 +3107,11 @@
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H102" s="6" t="n">
-        <v>-0.1200000001117587</v>
+        <v>0.6799999997019768</v>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
@@ -3124,66 +3122,66 @@
     <row r="103">
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>PMP1276988</t>
+          <t>PMP1277142</t>
         </is>
       </c>
       <c r="E103" s="6" t="n">
-        <v>-182382</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G103" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>-182382</v>
+        <v>1.100000023841858</v>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276988</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>PMP1276990</t>
+          <t>PMP1277144</t>
         </is>
       </c>
       <c r="E104" s="6" t="n">
-        <v>-538091</v>
+        <v>371.5</v>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H104" s="6" t="n">
-        <v>-538091</v>
+        <v>371.5</v>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276990</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -3195,11 +3193,11 @@
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>PMP1276990</t>
+          <t>PMP1277145</t>
         </is>
       </c>
       <c r="E105" s="6" t="n">
-        <v>-3.459999993443489</v>
+        <v>46.24000000022352</v>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
@@ -3208,11 +3206,11 @@
       </c>
       <c r="G105" s="10" t="inlineStr">
         <is>
-          <t>WOB</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>-3.459999993443489</v>
+        <v>46.24000000022352</v>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
@@ -3223,33 +3221,33 @@
     <row r="106">
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>PMP1276991</t>
+          <t>PMP1273112</t>
         </is>
       </c>
       <c r="E106" s="6" t="n">
-        <v>-375295</v>
+        <v>-2.120000001043081</v>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H106" s="6" t="n">
-        <v>-375295</v>
+        <v>-2.120000001043081</v>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276991</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -3261,11 +3259,11 @@
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>PMP1276991</t>
+          <t>PMP1273596</t>
         </is>
       </c>
       <c r="E107" s="6" t="n">
-        <v>-1.019999999552965</v>
+        <v>-0.8000000007450581</v>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
@@ -3278,7 +3276,7 @@
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>-1.019999999552965</v>
+        <v>-0.8000000007450581</v>
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
@@ -3289,132 +3287,132 @@
     <row r="108">
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>PMP1276992</t>
+          <t>PMP1273863</t>
         </is>
       </c>
       <c r="E108" s="6" t="n">
-        <v>-4956</v>
+        <v>-1.96000000089407</v>
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H108" s="6" t="n">
-        <v>-4956</v>
+        <v>-1.96000000089407</v>
       </c>
       <c r="I108" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1276992</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>PMP1277137</t>
+          <t>PMP1276666</t>
         </is>
       </c>
       <c r="E109" s="6" t="n">
-        <v>-973783</v>
+        <v>-0.7800000011920929</v>
       </c>
       <c r="F109" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G109" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H109" s="6" t="n">
-        <v>-973783</v>
+        <v>-0.7800000011920929</v>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1277137</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>PMP1277142</t>
+          <t>PMP1276673</t>
         </is>
       </c>
       <c r="E110" s="6" t="n">
-        <v>-1272672</v>
+        <v>-0.1200000001117587</v>
       </c>
       <c r="F110" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H110" s="6" t="n">
-        <v>-1272672</v>
+        <v>-0.1200000001117587</v>
       </c>
       <c r="I110" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1277142</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>PMP1277143</t>
+          <t>PMP1276990</t>
         </is>
       </c>
       <c r="E111" s="6" t="n">
-        <v>-18833393</v>
+        <v>-3.459999993443489</v>
       </c>
       <c r="F111" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
       <c r="G111" s="10" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>WOB</t>
         </is>
       </c>
       <c r="H111" s="6" t="n">
-        <v>-18833393</v>
+        <v>-3.459999993443489</v>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>Reduc Factura Compra PMP1277143</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
@@ -3426,11 +3424,11 @@
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>PMP1277143</t>
+          <t>PMP1276991</t>
         </is>
       </c>
       <c r="E112" s="6" t="n">
-        <v>-2.060000002384186</v>
+        <v>-1.019999999552965</v>
       </c>
       <c r="F112" s="10" t="inlineStr">
         <is>
@@ -3443,7 +3441,7 @@
         </is>
       </c>
       <c r="H112" s="6" t="n">
-        <v>-2.060000002384186</v>
+        <v>-1.019999999552965</v>
       </c>
       <c r="I112" s="11" t="inlineStr">
         <is>
@@ -3454,31 +3452,33 @@
     <row r="113">
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Nota</t>
+          <t>Descuentos no asociados a FC</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PMP1277143</t>
         </is>
       </c>
       <c r="E113" s="6" t="n">
-        <v>-82067413</v>
+        <v>-2.060000002384186</v>
       </c>
       <c r="F113" s="10" t="inlineStr">
         <is>
-          <t>DESCUENTO</t>
-        </is>
-      </c>
-      <c r="G113" s="10" t="n">
-        <v>987</v>
+          <t>MENORES VALORES</t>
+        </is>
+      </c>
+      <c r="G113" s="10" t="inlineStr">
+        <is>
+          <t>WOB</t>
+        </is>
       </c>
       <c r="H113" s="6" t="n">
-        <v>-82067413</v>
+        <v>-2.060000002384186</v>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>DDPD UNILEVER MIN 2Q 2025</t>
+          <t>MENORES VALORES</t>
         </is>
       </c>
     </row>
